--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -144,6 +144,15 @@
   </si>
   <si>
     <t>Tag@Chess.xlsx</t>
+  </si>
+  <si>
+    <t>Chess_TypeProperty</t>
+  </si>
+  <si>
+    <t>Chess_TypePropertyItem</t>
+  </si>
+  <si>
+    <t>TypeProperty@Chess.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1270,8 +1279,19 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="5:5">
-      <c r="E8" s="5"/>
+    <row r="8" customFormat="1" spans="2:5">
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="9" customFormat="1" spans="5:5">
       <c r="E9" s="5"/>
@@ -1474,6 +1494,7 @@
     <hyperlink ref="E5" r:id="rId2" display="Group@Chess.xlsx" tooltip="mailto:Group@Chess.xlsx"/>
     <hyperlink ref="E6" r:id="rId3" display="Initial@Chess.xlsx" tooltip="mailto:Initial@Chess.xlsx"/>
     <hyperlink ref="E7" r:id="rId4" display="Tag@Chess.xlsx" tooltip="mailto:Tag@Chess.xlsx"/>
+    <hyperlink ref="E8" r:id="rId5" display="TypeProperty@Chess.xlsx" tooltip="mailto:TypeProperty@Chess.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
